--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daowen/Documents/GitHub/Sarah-Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{431B4A43-D4A3-E748-AE32-64FA80BC59AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFBAEDA-E9B5-4F4D-817E-053551C089A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2401,7 +2401,7 @@
         <v>34</v>
       </c>
       <c r="C8" s="53">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D8" s="53">
         <v>0.48958333333333331</v>
@@ -3757,6 +3757,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -4122,7 +4123,7 @@
       </c>
       <c r="C10" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D10" s="58">
         <f ca="1"/>
@@ -4768,7 +4769,7 @@
       </c>
       <c r="C27" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D27" s="58">
         <f ca="1"/>
@@ -5414,7 +5415,7 @@
       </c>
       <c r="C44" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D44" s="58">
         <f ca="1"/>
@@ -5984,7 +5985,7 @@
       </c>
       <c r="C59" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D59" s="58">
         <f ca="1"/>
@@ -6554,7 +6555,7 @@
       </c>
       <c r="C74" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D74" s="58">
         <f ca="1"/>
@@ -7086,7 +7087,7 @@
       </c>
       <c r="C88" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D88" s="58">
         <f ca="1"/>
@@ -7618,7 +7619,7 @@
       </c>
       <c r="C102" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D102" s="58">
         <f ca="1"/>
@@ -8150,7 +8151,7 @@
       </c>
       <c r="C116" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D116" s="58">
         <f ca="1"/>
@@ -8682,7 +8683,7 @@
       </c>
       <c r="C130" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D130" s="58">
         <f ca="1"/>
@@ -9214,7 +9215,7 @@
       </c>
       <c r="C144" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D144" s="58">
         <f ca="1"/>
@@ -9746,7 +9747,7 @@
       </c>
       <c r="C158" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D158" s="58">
         <f ca="1"/>
@@ -10278,7 +10279,7 @@
       </c>
       <c r="C172" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D172" s="58">
         <f ca="1"/>
@@ -10810,7 +10811,7 @@
       </c>
       <c r="C186" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D186" s="58">
         <f ca="1"/>
@@ -11342,7 +11343,7 @@
       </c>
       <c r="C200" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D200" s="58">
         <f ca="1"/>
@@ -11874,7 +11875,7 @@
       </c>
       <c r="C214" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D214" s="58">
         <f ca="1"/>
@@ -12406,7 +12407,7 @@
       </c>
       <c r="C228" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D228" s="58">
         <f ca="1"/>
@@ -12938,7 +12939,7 @@
       </c>
       <c r="C242" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D242" s="58">
         <f ca="1"/>
@@ -13470,7 +13471,7 @@
       </c>
       <c r="C256" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D256" s="58">
         <f ca="1"/>
@@ -14002,7 +14003,7 @@
       </c>
       <c r="C270" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D270" s="58">
         <f ca="1"/>
@@ -14534,7 +14535,7 @@
       </c>
       <c r="C284" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D284" s="58">
         <f ca="1"/>
@@ -15066,7 +15067,7 @@
       </c>
       <c r="C298" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D298" s="58">
         <f ca="1"/>
@@ -15598,7 +15599,7 @@
       </c>
       <c r="C312" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D312" s="58">
         <f ca="1"/>
@@ -16130,7 +16131,7 @@
       </c>
       <c r="C326" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D326" s="58">
         <f ca="1"/>
@@ -16662,7 +16663,7 @@
       </c>
       <c r="C340" s="58">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D340" s="58">
         <f ca="1"/>
@@ -17194,7 +17195,7 @@
       </c>
       <c r="C354" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D354" s="60">
         <f ca="1"/>
@@ -17726,7 +17727,7 @@
       </c>
       <c r="C368" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D368" s="60">
         <f ca="1"/>
@@ -18258,7 +18259,7 @@
       </c>
       <c r="C382" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D382" s="60">
         <f ca="1"/>
@@ -18790,7 +18791,7 @@
       </c>
       <c r="C396" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D396" s="60">
         <f ca="1"/>
@@ -19322,7 +19323,7 @@
       </c>
       <c r="C410" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D410" s="60">
         <f ca="1"/>
@@ -19854,7 +19855,7 @@
       </c>
       <c r="C424" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D424" s="60">
         <f ca="1"/>
@@ -20386,7 +20387,7 @@
       </c>
       <c r="C438" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D438" s="60">
         <f ca="1"/>
@@ -20918,7 +20919,7 @@
       </c>
       <c r="C452" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D452" s="60">
         <f ca="1"/>
@@ -21450,7 +21451,7 @@
       </c>
       <c r="C466" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D466" s="60">
         <f ca="1"/>
@@ -21982,7 +21983,7 @@
       </c>
       <c r="C480" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D480" s="60">
         <f ca="1"/>
@@ -22514,7 +22515,7 @@
       </c>
       <c r="C494" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D494" s="60">
         <f ca="1"/>
@@ -23046,7 +23047,7 @@
       </c>
       <c r="C508" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D508" s="60">
         <f ca="1"/>
@@ -23578,7 +23579,7 @@
       </c>
       <c r="C522" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D522" s="60">
         <f ca="1"/>
@@ -24110,7 +24111,7 @@
       </c>
       <c r="C536" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D536" s="60">
         <f ca="1"/>
@@ -24642,7 +24643,7 @@
       </c>
       <c r="C550" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D550" s="60">
         <f ca="1"/>
@@ -25174,7 +25175,7 @@
       </c>
       <c r="C564" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D564" s="60">
         <f ca="1"/>
@@ -25706,7 +25707,7 @@
       </c>
       <c r="C578" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D578" s="60">
         <f ca="1"/>
@@ -26238,7 +26239,7 @@
       </c>
       <c r="C592" s="60">
         <f ca="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D592" s="60">
         <f ca="1"/>
@@ -26740,7 +26741,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="3.472222222222222E-3" right="3.472222222222222E-3" top="6.9444444444444441E-3" bottom="6.9444444444444441E-3" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="47" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daowen/Documents/GitHub/Sarah-Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827A3C24-9DC3-7146-94BB-BFD7F3D29A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C517E1-9006-9B40-B3F1-6A47F9A39B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="91">
   <si>
     <t>Event</t>
   </si>
@@ -966,41 +966,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFD9EAF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="29">
     <dxf>
       <fill>
         <patternFill patternType="gray0625"/>
@@ -1507,36 +1473,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{274ABB8C-71AA-4DDC-9E91-C988C50BBAF6}" name="SpecialEvents" displayName="SpecialEvents" ref="A1:H18" totalsRowShown="0" headerRowDxfId="32" dataDxfId="30" headerRowBorderDxfId="31" tableBorderDxfId="29" totalsRowBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{274ABB8C-71AA-4DDC-9E91-C988C50BBAF6}" name="SpecialEvents" displayName="SpecialEvents" ref="A1:H18" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
   <autoFilter ref="A1:H18" xr:uid="{274ABB8C-71AA-4DDC-9E91-C988C50BBAF6}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H5">
     <sortCondition ref="B1:B5"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{1E2F661C-419D-4A02-82EE-7487B03F56F8}" name="Event" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{AABEF517-D206-4E9B-9312-DFE8D9A8602C}" name="Date" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{12128115-A314-4B73-8B53-E3C7B82C699C}" name="Start Time" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{7B1D8727-3394-48EC-A1F0-E433D322B432}" name="End Time" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{B19CE393-3453-4412-B10F-BD7A1E362BA9}" name="Location" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{584DE6FB-4D7E-489B-8352-8B5F6AB2609E}" name="Category" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{D071B1C1-EB37-4663-9C1A-D83905550240}" name="Event Type" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{3D146997-928A-4259-9074-198D5AD77967}" name="Details" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{1E2F661C-419D-4A02-82EE-7487B03F56F8}" name="Event" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{AABEF517-D206-4E9B-9312-DFE8D9A8602C}" name="Date" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{12128115-A314-4B73-8B53-E3C7B82C699C}" name="Start Time" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{7B1D8727-3394-48EC-A1F0-E433D322B432}" name="End Time" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{B19CE393-3453-4412-B10F-BD7A1E362BA9}" name="Location" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{584DE6FB-4D7E-489B-8352-8B5F6AB2609E}" name="Category" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{D071B1C1-EB37-4663-9C1A-D83905550240}" name="Event Type" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{3D146997-928A-4259-9074-198D5AD77967}" name="Details" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2AE03B52-8C62-4C1F-AEDC-48B7B49B6D5B}" name="RecurringEvents" displayName="RecurringEvents" ref="A1:G15" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2AE03B52-8C62-4C1F-AEDC-48B7B49B6D5B}" name="RecurringEvents" displayName="RecurringEvents" ref="A1:G15" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="A1:G15" xr:uid="{2AE03B52-8C62-4C1F-AEDC-48B7B49B6D5B}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{8602A9D6-CC57-49FD-A5FA-5B193F42002B}" name="Event" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{34BEFA06-4FA5-4945-AD8D-DFBE54A76964}" name="Recurs On" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{83B7C080-F96E-4B1F-817F-115D2AB4EE43}" name="Start Time" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{E03A17BC-F31E-41FB-91B9-CD10FCABBC3C}" name="End Time" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{5FDCDD1C-4AA1-4523-8378-804574F70A30}" name="Location" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{584D187D-6964-48A8-B8B9-80A2BB3A46F1}" name="Category" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{0DD87F5B-9DE8-4040-89AB-02B6FB2448AC}" name="Event Type" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{8602A9D6-CC57-49FD-A5FA-5B193F42002B}" name="Event" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{34BEFA06-4FA5-4945-AD8D-DFBE54A76964}" name="Recurs On" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{83B7C080-F96E-4B1F-817F-115D2AB4EE43}" name="Start Time" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{E03A17BC-F31E-41FB-91B9-CD10FCABBC3C}" name="End Time" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{5FDCDD1C-4AA1-4523-8378-804574F70A30}" name="Location" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{584D187D-6964-48A8-B8B9-80A2BB3A46F1}" name="Category" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{0DD87F5B-9DE8-4040-89AB-02B6FB2448AC}" name="Event Type" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1566,7 +1532,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B85BA15A-547A-4A6A-BA7C-C4443E9DF620}" name="SpecialEventTimeOptions" displayName="SpecialEventTimeOptions" ref="C4:C80" totalsRowShown="0">
   <autoFilter ref="C4:C80" xr:uid="{B85BA15A-547A-4A6A-BA7C-C4443E9DF620}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9F4F56FF-0C21-4D3E-9395-BBED7485E489}" name="Time Slots" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{9F4F56FF-0C21-4D3E-9395-BBED7485E489}" name="Time Slots" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2172,7 +2138,9 @@
       <c r="D16" s="49">
         <v>0.53125</v>
       </c>
-      <c r="E16" s="44"/>
+      <c r="E16" s="44" t="s">
+        <v>71</v>
+      </c>
       <c r="F16" s="44" t="s">
         <v>10</v>
       </c>
@@ -2194,7 +2162,9 @@
       <c r="D17" s="49">
         <v>0.82291666666666663</v>
       </c>
-      <c r="E17" s="44"/>
+      <c r="E17" s="44" t="s">
+        <v>71</v>
+      </c>
       <c r="F17" s="44" t="s">
         <v>10</v>
       </c>
@@ -3975,9 +3945,9 @@
         <f ca="1"/>
         <v>0.82291666666666663</v>
       </c>
-      <c r="E5" s="17">
-        <f ca="1"/>
-        <v>0</v>
+      <c r="E5" s="17" t="str">
+        <f ca="1"/>
+        <v>DB</v>
       </c>
       <c r="F5" s="17" t="str">
         <f ca="1"/>
@@ -26552,18 +26522,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:H600">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>AND($B2&lt;&gt;"",MOD(SUMPRODUCT(($I$2:$I2&lt;&gt;$I$1:$I1)*1),2)=1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>AND($B2&lt;&gt;"",MOD(SUMPRODUCT(($I$2:$I2&lt;&gt;$I$1:$I1)*1),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>AND($B2&lt;&gt;"",SUMPRODUCT(($I$2:$I$600=$I2)*(ROW($I$2:$I$600)&lt;&gt;ROW())*($C$2:$C$600&lt;($D2+TIME(0,30,0)))*(($D$2:$D$600+TIME(0,30,0))&gt;$C2))&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:H610">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND($I2&lt;&gt;"",COUNTIF(INDIRECT("'School holiday'!$B$2:$B$150"),$I2)&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
